--- a/forms/trg/Formulir_TRG_blu-eco.xlsx
+++ b/forms/trg/Formulir_TRG_blu-eco.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B32)</f>
+        <f>COUNTA(Anggota!B5:B33)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F32)</f>
+        <f>COUNTA(Anggota!F5:F33)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,20 +913,20 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Darmawan Salman</t>
+          <t>Dr. Hasmin</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="n"/>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>Human Resources Management || Economics || Management || Resource Economic Valuation</t>
+        </is>
+      </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -934,12 +934,12 @@
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6713930</t>
+          <t>6011314</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>55614228900</t>
+          <t>57207449718</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Eymal Bashar Demmallino</t>
+          <t>Prof. Darmawan Salman</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -975,12 +975,12 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>6088441</t>
+          <t>6713930</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57207470700</t>
+          <t>55614228900</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Wadzibah Nas</t>
+          <t>Prof. Eymal Bashar Demmallino</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1016,12 +1016,12 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6808199</t>
+          <t>6088441</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>58510371800</t>
+          <t>57207470700</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Ir. Darhamsyah</t>
+          <t>Dr. Wadzibah Nas</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1054,19 +1054,15 @@
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
-      <c r="J8" s="11" t="inlineStr">
-        <is>
-          <t>0009-0007-8311-6429</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6956085</t>
+          <t>6808199</t>
         </is>
       </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>58725397900</t>
+          <t>58510371800</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1081,17 +1077,17 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Dr. Lucio Marcal Gomes</t>
+          <t>Dr. Ir. Darhamsyah</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>East Timor Coffee Institute (ETCI) Timor Leste</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E9" s="11" t="n"/>
@@ -1099,11 +1095,19 @@
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0009-0007-8311-6429</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6956085</t>
+        </is>
+      </c>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>58520195600</t>
+          <t>58725397900</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1118,17 +1122,17 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Hardiyono</t>
+          <t>Dr. Lucio Marcal Gomes</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Universitas Megarezky</t>
+          <t>East Timor Coffee Institute (ETCI) Timor Leste</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1138,7 +1142,11 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
+      <c r="L10" s="11" t="inlineStr">
+        <is>
+          <t>58520195600</t>
+        </is>
+      </c>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1151,17 +1159,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Ramalhino Lelo da Cruz</t>
+          <t>Dr. Hardiyono</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University\'</t>
+          <t>Universitas Megarezky</t>
         </is>
       </c>
       <c r="E11" s="11" t="n"/>
@@ -1184,17 +1192,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Sudarianto</t>
+          <t>Ramalhino Lelo da Cruz</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Hasanuddin University\'</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -1217,12 +1225,12 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Muthmainnah Aras</t>
+          <t>Sudarianto</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
@@ -1250,12 +1258,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Seniarfan</t>
+          <t>Muthmainnah Aras</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1283,12 +1291,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Jusri Yusuf</t>
+          <t>Seniarfan</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1316,12 +1324,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Ahmad Syafii Hafid</t>
+          <t>Jusri Yusuf</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1349,12 +1357,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Erwin</t>
+          <t>Ahmad Syafii Hafid</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1382,12 +1390,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Lidya Arlini</t>
+          <t>Erwin</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1415,12 +1423,12 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Pedro M. Da Costa</t>
+          <t>Lidya Arlini</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
@@ -1448,12 +1456,12 @@
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>Nur Magefirah Hamid</t>
+          <t>Pedro M. Da Costa</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
@@ -1479,10 +1487,26 @@
       <c r="A21" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="11" t="n"/>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Nur Magefirah Hamid</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>The Blue Economics Research Group is committed to advancing sustainable blue economy practices in Indonesia through high-impact research, innovation, and community empowerment. Our mission is to support public policy, enhance human resource capacity, and develop research-driven solutions that benefit coastal communities and marine ecosystems. We focus on key areas such as sustainable aquaculture, climate change adaptation, eco-friendly marine tourism, renewable ocean energy, and marine conservation. By fostering strategic partnerships with national and international stakeholders, we aim to drive sustainable economic growth while ensuring the long-term resilience of Indonesia’s marine and coastal resources.</t>
+        </is>
+      </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="12" t="n"/>
       <c r="H21" s="12" t="n"/>
@@ -1490,7 +1514,11 @@
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
       <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -1679,15 +1707,32 @@
       <c r="L32" s="12" t="n"/>
       <c r="M32" s="12" t="n"/>
     </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
